--- a/train_data.xlsx
+++ b/train_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dan\Desktop\Documents\Misc Documents\Other\Code Projects\darts_kpi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dan\Desktop\Documents\Code Projects\darts_kpi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2534419-37BF-44D8-ADF4-0607F330F413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8889EFD-AF46-4F83-872B-47C14AE3FF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A8BC78E0-9184-44D4-A991-72298E643C28}"/>
   </bookViews>
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">games!$A$1:$L$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">practice!$A$1:$I$36</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="39">
   <si>
     <t>Triple</t>
   </si>
@@ -137,7 +138,16 @@
     <t>6 (2.25)</t>
   </si>
   <si>
-    <t>Bed to Bull</t>
+    <t>Bed, Trip, Bull, Cricket, Double</t>
+  </si>
+  <si>
+    <t>Trip, Bed, Bull, Cricket, Double</t>
+  </si>
+  <si>
+    <t>Bed, Trip, Bull, Double, Cricket</t>
+  </si>
+  <si>
+    <t>11 (50.28)</t>
   </si>
 </sst>
 </file>
@@ -958,102 +968,435 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
+      <c r="A20" s="5">
+        <v>45521</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>61</v>
+      </c>
+      <c r="G20">
+        <v>16</v>
+      </c>
+      <c r="H20">
+        <v>93</v>
+      </c>
+      <c r="I20">
+        <v>99</v>
+      </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
+      <c r="A21" s="5">
+        <v>45573</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>12</v>
+      </c>
+      <c r="H21">
+        <v>12</v>
+      </c>
+      <c r="I21">
+        <v>99</v>
+      </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
+      <c r="A22" s="5">
+        <v>45580</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <v>19</v>
+      </c>
+      <c r="F22">
+        <v>63</v>
+      </c>
+      <c r="G22">
+        <v>7</v>
+      </c>
+      <c r="H22">
+        <v>83</v>
+      </c>
+      <c r="I22">
+        <v>99</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
+      <c r="A23" s="5">
+        <v>45584</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23">
+        <v>23</v>
+      </c>
+      <c r="H23">
+        <v>32</v>
+      </c>
+      <c r="I23">
+        <v>99</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="5">
+        <v>45586</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24">
+        <v>109</v>
+      </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
+      <c r="A25" s="5">
+        <v>45590</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>20</v>
+      </c>
+      <c r="F25">
+        <v>68</v>
+      </c>
+      <c r="G25">
+        <v>15</v>
+      </c>
+      <c r="H25">
+        <v>99</v>
+      </c>
+      <c r="I25">
+        <v>99</v>
+      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
+      <c r="A26" s="5">
+        <v>45593</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>17</v>
+      </c>
+      <c r="H26">
+        <v>17</v>
+      </c>
+      <c r="I26">
+        <v>99</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
+      <c r="A27" s="5">
+        <v>45598</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27">
+        <v>18</v>
+      </c>
+      <c r="F27">
+        <v>52</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>57</v>
+      </c>
+      <c r="I27">
+        <v>99</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
+      <c r="A28" s="5">
+        <v>45600</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28">
+        <v>25</v>
+      </c>
+      <c r="H28">
+        <v>32</v>
+      </c>
+      <c r="I28">
+        <v>99</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
+      <c r="A29" s="5">
+        <v>45604</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>18</v>
+      </c>
+      <c r="F29">
+        <v>54</v>
+      </c>
+      <c r="G29">
+        <v>11</v>
+      </c>
+      <c r="H29">
+        <v>76</v>
+      </c>
+      <c r="I29">
+        <v>99</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
+      <c r="A30" s="5">
+        <v>45617</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30">
+        <v>77</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
+      <c r="A31" s="5">
+        <v>45619</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31">
+        <v>87</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>45621</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="s">
+        <v>37</v>
+      </c>
+      <c r="I32">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>45623</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>45628</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
+        <v>37</v>
+      </c>
+      <c r="I34">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="5">
+        <v>45640</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35">
+        <v>14</v>
+      </c>
+      <c r="H35">
+        <v>14</v>
+      </c>
+      <c r="I35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>45641</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" t="s">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>16</v>
+      </c>
+      <c r="F36">
+        <v>65</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
+      </c>
+      <c r="H36">
+        <v>76</v>
+      </c>
+      <c r="I36">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I36" xr:uid="{49AC3371-D799-4ECC-9874-0415C330E239}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3192,121 +3535,880 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="5"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="3"/>
+      <c r="A57" s="5">
+        <v>45611</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1</v>
+      </c>
+      <c r="D57" t="s">
+        <v>32</v>
+      </c>
+      <c r="E57" t="s">
+        <v>33</v>
+      </c>
+      <c r="F57" t="s">
+        <v>34</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57" s="6">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="J57" s="6">
+        <v>3</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="5"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="3"/>
+      <c r="A58" s="5">
+        <v>45611</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" s="3">
+        <v>2</v>
+      </c>
+      <c r="D58" t="s">
+        <v>32</v>
+      </c>
+      <c r="E58" t="s">
+        <v>33</v>
+      </c>
+      <c r="F58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <v>2</v>
+      </c>
+      <c r="J58" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="3"/>
+      <c r="A59" s="5">
+        <v>45611</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" s="3">
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>32</v>
+      </c>
+      <c r="E59" t="s">
+        <v>33</v>
+      </c>
+      <c r="F59" t="s">
+        <v>34</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59" s="6">
+        <v>1.55</v>
+      </c>
+      <c r="J59" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="3"/>
+      <c r="A60" s="5">
+        <v>45614</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
+      <c r="D60" t="s">
+        <v>32</v>
+      </c>
+      <c r="E60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" t="s">
+        <v>34</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="I60" s="6">
+        <v>2.31</v>
+      </c>
+      <c r="J60" s="6">
+        <v>2</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="3"/>
+      <c r="A61" s="5">
+        <v>45614</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61" s="3">
+        <v>2</v>
+      </c>
+      <c r="D61" t="s">
+        <v>32</v>
+      </c>
+      <c r="E61" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" t="s">
+        <v>34</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61" s="6">
+        <v>1.55</v>
+      </c>
+      <c r="J61" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="3"/>
+      <c r="A62" s="5">
+        <v>45614</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="3">
+        <v>3</v>
+      </c>
+      <c r="D62" t="s">
+        <v>32</v>
+      </c>
+      <c r="E62" t="s">
+        <v>33</v>
+      </c>
+      <c r="F62" t="s">
+        <v>34</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62" s="6">
+        <v>2.27</v>
+      </c>
+      <c r="J62" s="6">
+        <v>3</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="3"/>
+      <c r="A63" s="5">
+        <v>45632</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63" s="3">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>501</v>
+      </c>
+      <c r="E63" t="s">
+        <v>29</v>
+      </c>
+      <c r="F63" t="s">
+        <v>38</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K63">
+        <v>55.67</v>
+      </c>
+      <c r="L63">
+        <v>61</v>
+      </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="3"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="3"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="3"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="3"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="3"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="3"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="3"/>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="3"/>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="3"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="3"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="3"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="3"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="3"/>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="3"/>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="3"/>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="3"/>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>45632</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="3">
+        <v>2</v>
+      </c>
+      <c r="D64">
+        <v>501</v>
+      </c>
+      <c r="E64" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64" t="s">
+        <v>38</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K64">
+        <v>57.81</v>
+      </c>
+      <c r="L64">
+        <v>50.33</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>45632</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" s="3">
+        <v>3</v>
+      </c>
+      <c r="D65">
+        <v>501</v>
+      </c>
+      <c r="E65" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65" t="s">
+        <v>38</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K65">
+        <v>48.7</v>
+      </c>
+      <c r="L65">
+        <v>44.33</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>45632</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" s="3">
+        <v>4</v>
+      </c>
+      <c r="D66">
+        <v>501</v>
+      </c>
+      <c r="E66" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66" t="s">
+        <v>38</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K66">
+        <v>38.380000000000003</v>
+      </c>
+      <c r="L66">
+        <v>61.33</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>45634</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1</v>
+      </c>
+      <c r="D67">
+        <v>501</v>
+      </c>
+      <c r="E67" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67" t="s">
+        <v>38</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K67">
+        <v>35.21</v>
+      </c>
+      <c r="L67">
+        <v>47.67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>45634</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="3">
+        <v>2</v>
+      </c>
+      <c r="D68">
+        <v>501</v>
+      </c>
+      <c r="E68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F68" t="s">
+        <v>38</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K68">
+        <v>50.67</v>
+      </c>
+      <c r="L68">
+        <v>30.33</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>45634</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69" s="3">
+        <v>3</v>
+      </c>
+      <c r="D69">
+        <v>501</v>
+      </c>
+      <c r="E69" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69" t="s">
+        <v>38</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K69">
+        <v>44.64</v>
+      </c>
+      <c r="L69">
+        <v>57.33</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>45634</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" s="3">
+        <v>4</v>
+      </c>
+      <c r="D70">
+        <v>501</v>
+      </c>
+      <c r="E70" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70" t="s">
+        <v>38</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K70">
+        <v>40.630000000000003</v>
+      </c>
+      <c r="L70">
+        <v>36.67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>45634</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" s="3">
+        <v>5</v>
+      </c>
+      <c r="D71">
+        <v>501</v>
+      </c>
+      <c r="E71" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71" t="s">
+        <v>38</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K71">
+        <v>42.64</v>
+      </c>
+      <c r="L71">
+        <v>29.67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>45634</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" s="3">
+        <v>6</v>
+      </c>
+      <c r="D72">
+        <v>501</v>
+      </c>
+      <c r="E72" t="s">
+        <v>29</v>
+      </c>
+      <c r="F72" t="s">
+        <v>38</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K72">
+        <v>48.5</v>
+      </c>
+      <c r="L72">
+        <v>46.33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>45635</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" s="3">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>501</v>
+      </c>
+      <c r="E73" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73" t="s">
+        <v>38</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K73">
+        <v>41.91</v>
+      </c>
+      <c r="L73">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>45635</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" s="3">
+        <v>2</v>
+      </c>
+      <c r="D74">
+        <v>501</v>
+      </c>
+      <c r="E74" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74" t="s">
+        <v>38</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K74">
+        <v>49.67</v>
+      </c>
+      <c r="L74">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>45635</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C75" s="3">
+        <v>3</v>
+      </c>
+      <c r="D75">
+        <v>501</v>
+      </c>
+      <c r="E75" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75" t="s">
+        <v>38</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K75">
+        <v>71.569999999999993</v>
+      </c>
+      <c r="L75">
+        <v>70.33</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
+        <v>45635</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76" s="3">
+        <v>4</v>
+      </c>
+      <c r="D76">
+        <v>501</v>
+      </c>
+      <c r="E76" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" t="s">
+        <v>38</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K76">
+        <v>60.13</v>
+      </c>
+      <c r="L76">
+        <v>39.67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>45635</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" s="3">
+        <v>5</v>
+      </c>
+      <c r="D77">
+        <v>501</v>
+      </c>
+      <c r="E77" t="s">
+        <v>29</v>
+      </c>
+      <c r="F77" t="s">
+        <v>38</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K77">
+        <v>53.68</v>
+      </c>
+      <c r="L77">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>45636</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>501</v>
+      </c>
+      <c r="E78" t="s">
+        <v>29</v>
+      </c>
+      <c r="F78" t="s">
+        <v>38</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K78">
+        <v>49.7</v>
+      </c>
+      <c r="L78">
+        <v>92.33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>45636</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" s="3">
+        <v>2</v>
+      </c>
+      <c r="D79">
+        <v>501</v>
+      </c>
+      <c r="E79" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79" t="s">
+        <v>38</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K79">
+        <v>53.38</v>
+      </c>
+      <c r="L79">
+        <v>48.33</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="3"/>
